--- a/Data/2035/REPowerEU++/Input/Xlsx/Storage.xlsx
+++ b/Data/2035/REPowerEU++/Input/Xlsx/Storage.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D717"/>
+  <dimension ref="A1:D703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12332,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="D662" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="663">
@@ -12350,7 +12350,7 @@
         <v>2</v>
       </c>
       <c r="D663" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="664">
@@ -12368,7 +12368,7 @@
         <v>3</v>
       </c>
       <c r="D664" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="665">
@@ -12386,7 +12386,7 @@
         <v>4</v>
       </c>
       <c r="D665" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="666">
@@ -12404,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="D666" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="667">
@@ -12422,7 +12422,7 @@
         <v>6</v>
       </c>
       <c r="D667" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="668">
@@ -12440,7 +12440,7 @@
         <v>7</v>
       </c>
       <c r="D668" t="n">
-        <v>37739</v>
+        <v>44995</v>
       </c>
     </row>
     <row r="669">
@@ -12824,7 +12824,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -12836,13 +12836,13 @@
         <v>1</v>
       </c>
       <c r="D690" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -12854,13 +12854,13 @@
         <v>2</v>
       </c>
       <c r="D691" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -12872,13 +12872,13 @@
         <v>3</v>
       </c>
       <c r="D692" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -12890,13 +12890,13 @@
         <v>4</v>
       </c>
       <c r="D693" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -12908,13 +12908,13 @@
         <v>5</v>
       </c>
       <c r="D694" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -12926,13 +12926,13 @@
         <v>6</v>
       </c>
       <c r="D695" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -12944,13 +12944,13 @@
         <v>7</v>
       </c>
       <c r="D696" t="n">
-        <v>7256</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -12986,7 +12986,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -13004,7 +13004,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -13022,7 +13022,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -13040,7 +13040,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -13058,7 +13058,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -13070,258 +13070,6 @@
         <v>7</v>
       </c>
       <c r="D703" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C704" t="n">
-        <v>1</v>
-      </c>
-      <c r="D704" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C705" t="n">
-        <v>2</v>
-      </c>
-      <c r="D705" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C706" t="n">
-        <v>3</v>
-      </c>
-      <c r="D706" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C707" t="n">
-        <v>4</v>
-      </c>
-      <c r="D707" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C708" t="n">
-        <v>5</v>
-      </c>
-      <c r="D708" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C709" t="n">
-        <v>6</v>
-      </c>
-      <c r="D709" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C710" t="n">
-        <v>7</v>
-      </c>
-      <c r="D710" t="n">
-        <v>2827</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C711" t="n">
-        <v>1</v>
-      </c>
-      <c r="D711" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C712" t="n">
-        <v>2</v>
-      </c>
-      <c r="D712" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C713" t="n">
-        <v>3</v>
-      </c>
-      <c r="D713" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C714" t="n">
-        <v>4</v>
-      </c>
-      <c r="D714" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C715" t="n">
-        <v>5</v>
-      </c>
-      <c r="D715" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C716" t="n">
-        <v>6</v>
-      </c>
-      <c r="D716" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C717" t="n">
-        <v>7</v>
-      </c>
-      <c r="D717" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13336,7 +13084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14796,7 +14544,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>61593</v>
+        <v>72477</v>
       </c>
     </row>
     <row r="99">
@@ -14811,7 +14559,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>620000000</v>
+        <v>640000000</v>
       </c>
     </row>
     <row r="100">
@@ -14847,7 +14595,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -14856,13 +14604,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10884</v>
+        <v>4240.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -14871,36 +14619,6 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>4240.5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
         <v>20000000</v>
       </c>
     </row>
@@ -15751,7 +15469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D717"/>
+  <dimension ref="A1:D703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27655,7 +27373,7 @@
         <v>1</v>
       </c>
       <c r="D662" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="663">
@@ -27673,7 +27391,7 @@
         <v>2</v>
       </c>
       <c r="D663" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="664">
@@ -27691,7 +27409,7 @@
         <v>3</v>
       </c>
       <c r="D664" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="665">
@@ -27709,7 +27427,7 @@
         <v>4</v>
       </c>
       <c r="D665" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="666">
@@ -27727,7 +27445,7 @@
         <v>5</v>
       </c>
       <c r="D666" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="667">
@@ -27745,7 +27463,7 @@
         <v>6</v>
       </c>
       <c r="D667" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="668">
@@ -27763,7 +27481,7 @@
         <v>7</v>
       </c>
       <c r="D668" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="669">
@@ -27781,7 +27499,7 @@
         <v>1</v>
       </c>
       <c r="D669" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="670">
@@ -27799,7 +27517,7 @@
         <v>2</v>
       </c>
       <c r="D670" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="671">
@@ -27817,7 +27535,7 @@
         <v>3</v>
       </c>
       <c r="D671" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="672">
@@ -27835,7 +27553,7 @@
         <v>4</v>
       </c>
       <c r="D672" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="673">
@@ -27853,7 +27571,7 @@
         <v>5</v>
       </c>
       <c r="D673" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="674">
@@ -27871,7 +27589,7 @@
         <v>6</v>
       </c>
       <c r="D674" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="675">
@@ -27889,7 +27607,7 @@
         <v>7</v>
       </c>
       <c r="D675" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="676">
@@ -28147,7 +27865,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -28165,7 +27883,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -28183,7 +27901,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -28201,7 +27919,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -28219,7 +27937,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -28237,7 +27955,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -28255,7 +27973,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -28273,7 +27991,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -28291,7 +28009,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -28309,7 +28027,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -28327,7 +28045,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -28345,7 +28063,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -28363,7 +28081,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -28381,7 +28099,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -28393,258 +28111,6 @@
         <v>7</v>
       </c>
       <c r="D703" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C704" t="n">
-        <v>1</v>
-      </c>
-      <c r="D704" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C705" t="n">
-        <v>2</v>
-      </c>
-      <c r="D705" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C706" t="n">
-        <v>3</v>
-      </c>
-      <c r="D706" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C707" t="n">
-        <v>4</v>
-      </c>
-      <c r="D707" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C708" t="n">
-        <v>5</v>
-      </c>
-      <c r="D708" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C709" t="n">
-        <v>6</v>
-      </c>
-      <c r="D709" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C710" t="n">
-        <v>7</v>
-      </c>
-      <c r="D710" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C711" t="n">
-        <v>1</v>
-      </c>
-      <c r="D711" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C712" t="n">
-        <v>2</v>
-      </c>
-      <c r="D712" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C713" t="n">
-        <v>3</v>
-      </c>
-      <c r="D713" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C714" t="n">
-        <v>4</v>
-      </c>
-      <c r="D714" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C715" t="n">
-        <v>5</v>
-      </c>
-      <c r="D715" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C716" t="n">
-        <v>6</v>
-      </c>
-      <c r="D716" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C717" t="n">
-        <v>7</v>
-      </c>
-      <c r="D717" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -29129,7 +28595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D717"/>
+  <dimension ref="A1:D703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41033,7 +40499,7 @@
         <v>1</v>
       </c>
       <c r="D662" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="663">
@@ -41051,7 +40517,7 @@
         <v>2</v>
       </c>
       <c r="D663" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="664">
@@ -41069,7 +40535,7 @@
         <v>3</v>
       </c>
       <c r="D664" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="665">
@@ -41087,7 +40553,7 @@
         <v>4</v>
       </c>
       <c r="D665" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="666">
@@ -41105,7 +40571,7 @@
         <v>5</v>
       </c>
       <c r="D666" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="667">
@@ -41123,7 +40589,7 @@
         <v>6</v>
       </c>
       <c r="D667" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="668">
@@ -41141,7 +40607,7 @@
         <v>7</v>
       </c>
       <c r="D668" t="n">
-        <v>740683.806</v>
+        <v>779309.806</v>
       </c>
     </row>
     <row r="669">
@@ -41525,7 +40991,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -41537,13 +41003,13 @@
         <v>1</v>
       </c>
       <c r="D690" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -41555,13 +41021,13 @@
         <v>2</v>
       </c>
       <c r="D691" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -41573,13 +41039,13 @@
         <v>3</v>
       </c>
       <c r="D692" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -41591,13 +41057,13 @@
         <v>4</v>
       </c>
       <c r="D693" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -41609,13 +41075,13 @@
         <v>5</v>
       </c>
       <c r="D694" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -41627,13 +41093,13 @@
         <v>6</v>
       </c>
       <c r="D695" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -41645,13 +41111,13 @@
         <v>7</v>
       </c>
       <c r="D696" t="n">
-        <v>38626</v>
+        <v>107254.08</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -41669,7 +41135,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -41687,7 +41153,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -41705,7 +41171,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -41723,7 +41189,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -41741,7 +41207,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -41759,7 +41225,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -41771,258 +41237,6 @@
         <v>7</v>
       </c>
       <c r="D703" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C704" t="n">
-        <v>1</v>
-      </c>
-      <c r="D704" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C705" t="n">
-        <v>2</v>
-      </c>
-      <c r="D705" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C706" t="n">
-        <v>3</v>
-      </c>
-      <c r="D706" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C707" t="n">
-        <v>4</v>
-      </c>
-      <c r="D707" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C708" t="n">
-        <v>5</v>
-      </c>
-      <c r="D708" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C709" t="n">
-        <v>6</v>
-      </c>
-      <c r="D709" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C710" t="n">
-        <v>7</v>
-      </c>
-      <c r="D710" t="n">
-        <v>107254.08</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C711" t="n">
-        <v>1</v>
-      </c>
-      <c r="D711" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C712" t="n">
-        <v>2</v>
-      </c>
-      <c r="D712" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C713" t="n">
-        <v>3</v>
-      </c>
-      <c r="D713" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C714" t="n">
-        <v>4</v>
-      </c>
-      <c r="D714" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C715" t="n">
-        <v>5</v>
-      </c>
-      <c r="D715" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C716" t="n">
-        <v>6</v>
-      </c>
-      <c r="D716" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C717" t="n">
-        <v>7</v>
-      </c>
-      <c r="D717" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42037,7 +41251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D717"/>
+  <dimension ref="A1:D703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53941,7 +53155,7 @@
         <v>1</v>
       </c>
       <c r="D662" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="663">
@@ -53959,7 +53173,7 @@
         <v>2</v>
       </c>
       <c r="D663" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="664">
@@ -53977,7 +53191,7 @@
         <v>3</v>
       </c>
       <c r="D664" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="665">
@@ -53995,7 +53209,7 @@
         <v>4</v>
       </c>
       <c r="D665" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="666">
@@ -54013,7 +53227,7 @@
         <v>5</v>
       </c>
       <c r="D666" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="667">
@@ -54031,7 +53245,7 @@
         <v>6</v>
       </c>
       <c r="D667" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="668">
@@ -54049,7 +53263,7 @@
         <v>7</v>
       </c>
       <c r="D668" t="n">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="669">
@@ -54067,7 +53281,7 @@
         <v>1</v>
       </c>
       <c r="D669" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="670">
@@ -54085,7 +53299,7 @@
         <v>2</v>
       </c>
       <c r="D670" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="671">
@@ -54103,7 +53317,7 @@
         <v>3</v>
       </c>
       <c r="D671" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="672">
@@ -54121,7 +53335,7 @@
         <v>4</v>
       </c>
       <c r="D672" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="673">
@@ -54139,7 +53353,7 @@
         <v>5</v>
       </c>
       <c r="D673" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="674">
@@ -54157,7 +53371,7 @@
         <v>6</v>
       </c>
       <c r="D674" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="675">
@@ -54175,7 +53389,7 @@
         <v>7</v>
       </c>
       <c r="D675" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="676">
@@ -54433,7 +53647,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -54451,7 +53665,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -54469,7 +53683,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -54487,7 +53701,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -54505,7 +53719,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -54523,7 +53737,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -54541,7 +53755,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -54559,7 +53773,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -54577,7 +53791,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -54595,7 +53809,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -54613,7 +53827,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -54631,7 +53845,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -54649,7 +53863,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -54667,7 +53881,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -54679,258 +53893,6 @@
         <v>7</v>
       </c>
       <c r="D703" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C704" t="n">
-        <v>1</v>
-      </c>
-      <c r="D704" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C705" t="n">
-        <v>2</v>
-      </c>
-      <c r="D705" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C706" t="n">
-        <v>3</v>
-      </c>
-      <c r="D706" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C707" t="n">
-        <v>4</v>
-      </c>
-      <c r="D707" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C708" t="n">
-        <v>5</v>
-      </c>
-      <c r="D708" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C709" t="n">
-        <v>6</v>
-      </c>
-      <c r="D709" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C710" t="n">
-        <v>7</v>
-      </c>
-      <c r="D710" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C711" t="n">
-        <v>1</v>
-      </c>
-      <c r="D711" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C712" t="n">
-        <v>2</v>
-      </c>
-      <c r="D712" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C713" t="n">
-        <v>3</v>
-      </c>
-      <c r="D713" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C714" t="n">
-        <v>4</v>
-      </c>
-      <c r="D714" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C715" t="n">
-        <v>5</v>
-      </c>
-      <c r="D715" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C716" t="n">
-        <v>6</v>
-      </c>
-      <c r="D716" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C717" t="n">
-        <v>7</v>
-      </c>
-      <c r="D717" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -54945,7 +53907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56405,7 +55367,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>948956.586</v>
+        <v>991445.186</v>
       </c>
     </row>
     <row r="99">
@@ -56420,7 +55382,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>620000000</v>
+        <v>640000000</v>
       </c>
     </row>
     <row r="100">
@@ -56456,7 +55418,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -56465,13 +55427,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>42488.6</v>
+        <v>117979.488</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -56480,36 +55442,6 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Hydro Pump Storage</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>117979.488</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Li-Ion_BESS</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
         <v>20000000</v>
       </c>
     </row>
